--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_ANADOLU EFES ISTANBUL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_ANADOLU EFES ISTANBUL.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>29.8572</v>
+        <v>31.1311</v>
       </c>
       <c r="E2" t="n">
-        <v>37.0013</v>
+        <v>13.6826</v>
       </c>
       <c r="F2" t="n">
-        <v>-7.144699999999999</v>
+        <v>17.4486</v>
       </c>
       <c r="G2" t="n">
-        <v>20.4283</v>
+        <v>35.1499</v>
       </c>
       <c r="H2" t="n">
-        <v>27.5364</v>
+        <v>2.637600000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.1079</v>
+        <v>32.5118</v>
       </c>
       <c r="J2" t="n">
-        <v>44.502</v>
+        <v>76.40299999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>33.0558</v>
+        <v>26.6007</v>
       </c>
       <c r="L2" t="n">
-        <v>11.4461</v>
+        <v>49.802</v>
       </c>
       <c r="M2" t="n">
-        <v>-24.0736</v>
+        <v>-41.2535</v>
       </c>
       <c r="N2" t="n">
-        <v>-5.519600000000001</v>
+        <v>-23.9631</v>
       </c>
       <c r="O2" t="n">
-        <v>-18.5541</v>
+        <v>-17.2902</v>
       </c>
       <c r="P2" t="n">
-        <v>16.0046</v>
+        <v>1.391799999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>-23.8916</v>
+        <v>-72.3695</v>
       </c>
       <c r="R2" t="n">
-        <v>39.8964</v>
+        <v>73.7611</v>
       </c>
       <c r="S2" t="n">
-        <v>16.1745</v>
+        <v>-4.843</v>
       </c>
       <c r="T2" t="n">
-        <v>11.6447</v>
+        <v>-10.312</v>
       </c>
       <c r="U2" t="n">
-        <v>4.5296</v>
+        <v>5.4688</v>
       </c>
       <c r="V2" t="n">
-        <v>-22.7512</v>
+        <v>-0.5670999999999995</v>
       </c>
       <c r="W2" t="n">
-        <v>4.7453</v>
+        <v>19.9601</v>
       </c>
       <c r="X2" t="n">
-        <v>-27.4965</v>
+        <v>-20.5272</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D3" t="n">
-        <v>18.1159</v>
+        <v>14.7875</v>
       </c>
       <c r="E3" t="n">
-        <v>5.874900000000001</v>
+        <v>24.8048</v>
       </c>
       <c r="F3" t="n">
-        <v>12.2411</v>
+        <v>-10.0174</v>
       </c>
       <c r="G3" t="n">
-        <v>35.1499</v>
+        <v>20.4283</v>
       </c>
       <c r="H3" t="n">
-        <v>2.637600000000001</v>
+        <v>27.5364</v>
       </c>
       <c r="I3" t="n">
-        <v>32.5118</v>
+        <v>-7.1079</v>
       </c>
       <c r="J3" t="n">
-        <v>76.40299999999999</v>
+        <v>44.502</v>
       </c>
       <c r="K3" t="n">
-        <v>26.6007</v>
+        <v>33.0558</v>
       </c>
       <c r="L3" t="n">
-        <v>49.802</v>
+        <v>11.4461</v>
       </c>
       <c r="M3" t="n">
-        <v>-41.2535</v>
+        <v>-24.0736</v>
       </c>
       <c r="N3" t="n">
-        <v>-23.9631</v>
+        <v>-5.519600000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-17.2902</v>
+        <v>-18.5541</v>
       </c>
       <c r="P3" t="n">
-        <v>1.391799999999999</v>
+        <v>16.0046</v>
       </c>
       <c r="Q3" t="n">
-        <v>-72.3695</v>
+        <v>-23.8916</v>
       </c>
       <c r="R3" t="n">
-        <v>73.7611</v>
+        <v>39.8964</v>
       </c>
       <c r="S3" t="n">
-        <v>-17.8586</v>
+        <v>1.1052</v>
       </c>
       <c r="T3" t="n">
-        <v>-18.12</v>
+        <v>-0.552</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2611999999999999</v>
+        <v>1.6567</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5670999999999995</v>
+        <v>-22.7512</v>
       </c>
       <c r="W3" t="n">
-        <v>19.9601</v>
+        <v>4.7453</v>
       </c>
       <c r="X3" t="n">
-        <v>-20.5272</v>
+        <v>-27.4965</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. POIRIER</t>
+          <t>S. LEE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>13.4488</v>
+        <v>10.8864</v>
       </c>
       <c r="E4" t="n">
-        <v>13.8596</v>
+        <v>8.4085</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4105000000000002</v>
+        <v>2.4777</v>
       </c>
       <c r="G4" t="n">
-        <v>-6.0556</v>
+        <v>3.095800000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-5.996499999999999</v>
+        <v>6.8002</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05900000000000039</v>
+        <v>-3.7043</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7892</v>
+        <v>16.4357</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.2468</v>
+        <v>11.4051</v>
       </c>
       <c r="L4" t="n">
-        <v>6.0359</v>
+        <v>5.030600000000002</v>
       </c>
       <c r="M4" t="n">
-        <v>-9.8447</v>
+        <v>-13.3399</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.7497</v>
+        <v>-4.605300000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.0949</v>
+        <v>-8.7349</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7833</v>
+        <v>1.1599</v>
       </c>
       <c r="Q4" t="n">
-        <v>-12.0616</v>
+        <v>-24.5872</v>
       </c>
       <c r="R4" t="n">
-        <v>14.8452</v>
+        <v>25.7469</v>
       </c>
       <c r="S4" t="n">
-        <v>15.9012</v>
+        <v>-7.0068</v>
       </c>
       <c r="T4" t="n">
-        <v>12.4197</v>
+        <v>-5.291700000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>3.4814</v>
+        <v>-1.7147</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8197000000000001</v>
+        <v>13.6376</v>
       </c>
       <c r="W4" t="n">
-        <v>9.712</v>
+        <v>21.8519</v>
       </c>
       <c r="X4" t="n">
-        <v>-8.892300000000001</v>
+        <v>-8.214399999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. LEE</t>
+          <t>S. LARKIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>5.519200000000001</v>
+        <v>9.448900000000002</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6764</v>
+        <v>6.2594</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1572000000000001</v>
+        <v>3.1896</v>
       </c>
       <c r="G5" t="n">
-        <v>3.095800000000001</v>
+        <v>9.047800000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8002</v>
+        <v>-1.1568</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.7043</v>
+        <v>10.2046</v>
       </c>
       <c r="J5" t="n">
-        <v>16.4357</v>
+        <v>28.0672</v>
       </c>
       <c r="K5" t="n">
-        <v>11.4051</v>
+        <v>7.438599999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>5.030600000000002</v>
+        <v>20.6286</v>
       </c>
       <c r="M5" t="n">
-        <v>-13.3399</v>
+        <v>-19.0195</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.605300000000001</v>
+        <v>-8.5951</v>
       </c>
       <c r="O5" t="n">
-        <v>-8.7349</v>
+        <v>-10.4244</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1599</v>
+        <v>-7.6545</v>
       </c>
       <c r="Q5" t="n">
-        <v>-24.5872</v>
+        <v>-35.2567</v>
       </c>
       <c r="R5" t="n">
-        <v>25.7469</v>
+        <v>27.6023</v>
       </c>
       <c r="S5" t="n">
-        <v>-12.3739</v>
+        <v>-2.6975</v>
       </c>
       <c r="T5" t="n">
-        <v>-8.0244</v>
+        <v>-2.6653</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.3494</v>
+        <v>-0.03210000000000002</v>
       </c>
       <c r="V5" t="n">
-        <v>13.6376</v>
+        <v>10.7531</v>
       </c>
       <c r="W5" t="n">
-        <v>21.8519</v>
+        <v>16.1141</v>
       </c>
       <c r="X5" t="n">
-        <v>-8.214399999999999</v>
+        <v>-5.361000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>2.166600000000002</v>
+        <v>5.710500000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>10.7056</v>
+        <v>12.9348</v>
       </c>
       <c r="F6" t="n">
-        <v>-8.5389</v>
+        <v>-7.2242</v>
       </c>
       <c r="G6" t="n">
         <v>7.1647</v>
@@ -922,13 +922,13 @@
         <v>17.1649</v>
       </c>
       <c r="S6" t="n">
-        <v>-9.5852</v>
+        <v>-6.041399999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-8.452999999999999</v>
+        <v>-6.2239</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1322</v>
+        <v>0.1822999999999999</v>
       </c>
       <c r="V6" t="n">
         <v>-3.5313</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. DESSERT</t>
+          <t>V. POIRIER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6044</v>
+        <v>3.445800000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>5.653700000000001</v>
+        <v>3.6172</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.0493</v>
+        <v>-0.1712999999999998</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1044</v>
+        <v>-6.0556</v>
       </c>
       <c r="H7" t="n">
-        <v>3.225099999999999</v>
+        <v>-5.996499999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.1207</v>
+        <v>-0.05900000000000039</v>
       </c>
       <c r="J7" t="n">
-        <v>12.3656</v>
+        <v>3.7892</v>
       </c>
       <c r="K7" t="n">
-        <v>10.4517</v>
+        <v>-2.2468</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9137</v>
+        <v>6.0359</v>
       </c>
       <c r="M7" t="n">
-        <v>-12.2614</v>
+        <v>-9.8447</v>
       </c>
       <c r="N7" t="n">
-        <v>-7.2269</v>
+        <v>-3.7497</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.0348</v>
+        <v>-6.0949</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3194</v>
+        <v>2.7833</v>
       </c>
       <c r="Q7" t="n">
-        <v>-19.0203</v>
+        <v>-12.0616</v>
       </c>
       <c r="R7" t="n">
-        <v>16.7009</v>
+        <v>14.8452</v>
       </c>
       <c r="S7" t="n">
-        <v>11.3252</v>
+        <v>5.8982</v>
       </c>
       <c r="T7" t="n">
-        <v>10.7794</v>
+        <v>2.1776</v>
       </c>
       <c r="U7" t="n">
-        <v>0.546</v>
+        <v>3.7206</v>
       </c>
       <c r="V7" t="n">
-        <v>-7.5054</v>
+        <v>0.8197000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5287</v>
+        <v>9.712</v>
       </c>
       <c r="X7" t="n">
-        <v>-9.0341</v>
+        <v>-8.892300000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LARKIN</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7359</v>
+        <v>-1.6835</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2354000000000003</v>
+        <v>-7.360899999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5004999999999997</v>
+        <v>5.677499999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>9.047800000000001</v>
+        <v>-26.8604</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1568</v>
+        <v>-10.8842</v>
       </c>
       <c r="I8" t="n">
-        <v>10.2046</v>
+        <v>-15.9755</v>
       </c>
       <c r="J8" t="n">
-        <v>28.0672</v>
+        <v>3.954000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>7.438599999999999</v>
+        <v>1.276100000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>20.6286</v>
+        <v>2.6776</v>
       </c>
       <c r="M8" t="n">
-        <v>-19.0195</v>
+        <v>-30.8136</v>
       </c>
       <c r="N8" t="n">
-        <v>-8.5951</v>
+        <v>-12.1606</v>
       </c>
       <c r="O8" t="n">
-        <v>-10.4244</v>
+        <v>-18.6536</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.6545</v>
+        <v>5.335</v>
       </c>
       <c r="Q8" t="n">
-        <v>-35.2567</v>
+        <v>-53.3492</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6023</v>
+        <v>58.6841</v>
       </c>
       <c r="S8" t="n">
-        <v>-12.8825</v>
+        <v>-1.3499</v>
       </c>
       <c r="T8" t="n">
-        <v>-9.160299999999999</v>
+        <v>-3.6588</v>
       </c>
       <c r="U8" t="n">
-        <v>-3.7221</v>
+        <v>2.3087</v>
       </c>
       <c r="V8" t="n">
-        <v>10.7531</v>
+        <v>21.1915</v>
       </c>
       <c r="W8" t="n">
-        <v>16.1141</v>
+        <v>45.6929</v>
       </c>
       <c r="X8" t="n">
-        <v>-5.361000000000001</v>
+        <v>-24.5014</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5441</v>
+        <v>-2.3125</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3201</v>
+        <v>-3.9219</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7761</v>
+        <v>1.6094</v>
       </c>
       <c r="G9" t="n">
         <v>-2.7514</v>
@@ -1156,13 +1156,13 @@
         <v>4.1753</v>
       </c>
       <c r="S9" t="n">
-        <v>2.0115</v>
+        <v>1.2432</v>
       </c>
       <c r="T9" t="n">
-        <v>1.035</v>
+        <v>0.4334</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9767000000000001</v>
+        <v>0.8098000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>-2.428</v>
@@ -1189,13 +1189,13 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5338</v>
+        <v>-4.1648</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6837000000000001</v>
+        <v>0.02409999999999973</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.8503</v>
+        <v>-4.1889</v>
       </c>
       <c r="G10" t="n">
         <v>0.4310000000000003</v>
@@ -1234,13 +1234,13 @@
         <v>1.3919</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1996</v>
+        <v>-0.8306</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6915</v>
+        <v>0.0163</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.5081</v>
+        <v>-0.8467</v>
       </c>
       <c r="V10" t="n">
         <v>-1.214</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>B. DESSERT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.723</v>
+        <v>-5.378</v>
       </c>
       <c r="E11" t="n">
-        <v>-23.5078</v>
+        <v>-2.025</v>
       </c>
       <c r="F11" t="n">
-        <v>11.7853</v>
+        <v>-3.352999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>1.5142</v>
+        <v>0.1044</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.428</v>
+        <v>3.225099999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>2.9416</v>
+        <v>-3.1207</v>
       </c>
       <c r="J11" t="n">
-        <v>36.9599</v>
+        <v>12.3656</v>
       </c>
       <c r="K11" t="n">
-        <v>14.977</v>
+        <v>10.4517</v>
       </c>
       <c r="L11" t="n">
-        <v>21.9826</v>
+        <v>1.9137</v>
       </c>
       <c r="M11" t="n">
-        <v>-35.4457</v>
+        <v>-12.2614</v>
       </c>
       <c r="N11" t="n">
-        <v>-16.4049</v>
+        <v>-7.2269</v>
       </c>
       <c r="O11" t="n">
-        <v>-19.0409</v>
+        <v>-5.0348</v>
       </c>
       <c r="P11" t="n">
-        <v>-22.9631</v>
+        <v>-2.3194</v>
       </c>
       <c r="Q11" t="n">
-        <v>-89.3017</v>
+        <v>-19.0203</v>
       </c>
       <c r="R11" t="n">
-        <v>66.3386</v>
+        <v>16.7009</v>
       </c>
       <c r="S11" t="n">
-        <v>12.0124</v>
+        <v>4.3424</v>
       </c>
       <c r="T11" t="n">
-        <v>4.0486</v>
+        <v>3.1007</v>
       </c>
       <c r="U11" t="n">
-        <v>7.9641</v>
+        <v>1.242</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.2862</v>
+        <v>-7.5054</v>
       </c>
       <c r="W11" t="n">
-        <v>24.785</v>
+        <v>1.5287</v>
       </c>
       <c r="X11" t="n">
-        <v>-27.0712</v>
+        <v>-9.0341</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>R. BEAUBOIS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.9012</v>
+        <v>-12.4851</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.4299</v>
+        <v>-8.000299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4712</v>
+        <v>-4.4846</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.9133</v>
+        <v>3.984699999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2342</v>
+        <v>1.6998</v>
       </c>
       <c r="I12" t="n">
-        <v>-9.147599999999999</v>
+        <v>2.284899999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2291999999999998</v>
+        <v>10.6006</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8874</v>
+        <v>7.3197</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.1164</v>
+        <v>3.280600000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.6843</v>
+        <v>-6.6158</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.6532</v>
+        <v>-5.6196</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.0308</v>
+        <v>-0.9958999999999997</v>
       </c>
       <c r="P12" t="n">
-        <v>9.999999999998899e-05</v>
+        <v>3.7114</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.7731</v>
+        <v>-13.6855</v>
       </c>
       <c r="R12" t="n">
-        <v>15.7733</v>
+        <v>17.3967</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9836999999999999</v>
+        <v>-7.6779</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0313</v>
+        <v>-7.5965</v>
       </c>
       <c r="U12" t="n">
-        <v>2.0156</v>
+        <v>-0.08180000000000003</v>
       </c>
       <c r="V12" t="n">
-        <v>-8.9719</v>
+        <v>-12.5032</v>
       </c>
       <c r="W12" t="n">
-        <v>4.6035</v>
+        <v>2.6805</v>
       </c>
       <c r="X12" t="n">
-        <v>-13.5754</v>
+        <v>-15.1837</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. BEAUBOIS</t>
+          <t>I. CORDINIER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D13" t="n">
-        <v>-17.2217</v>
+        <v>-12.8727</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.6269</v>
+        <v>-15.5107</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.595000000000001</v>
+        <v>2.637799999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>3.984699999999999</v>
+        <v>-10.7248</v>
       </c>
       <c r="H13" t="n">
-        <v>1.6998</v>
+        <v>0.2534999999999994</v>
       </c>
       <c r="I13" t="n">
-        <v>2.284899999999999</v>
+        <v>-10.9783</v>
       </c>
       <c r="J13" t="n">
-        <v>10.6006</v>
+        <v>13.8942</v>
       </c>
       <c r="K13" t="n">
-        <v>7.3197</v>
+        <v>14.8892</v>
       </c>
       <c r="L13" t="n">
-        <v>3.280600000000001</v>
+        <v>-0.9946999999999995</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.6158</v>
+        <v>-24.6192</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.6196</v>
+        <v>-14.6356</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.9958999999999997</v>
+        <v>-9.9842</v>
       </c>
       <c r="P13" t="n">
-        <v>3.7114</v>
+        <v>-2.783400000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-13.6855</v>
+        <v>-54.2771</v>
       </c>
       <c r="R13" t="n">
-        <v>17.3967</v>
+        <v>51.4937</v>
       </c>
       <c r="S13" t="n">
-        <v>-12.4149</v>
+        <v>-5.4038</v>
       </c>
       <c r="T13" t="n">
-        <v>-10.2224</v>
+        <v>-4.1713</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.192</v>
+        <v>-1.2321</v>
       </c>
       <c r="V13" t="n">
-        <v>-12.5032</v>
+        <v>6.0389</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6805</v>
+        <v>29.0427</v>
       </c>
       <c r="X13" t="n">
-        <v>-15.1837</v>
+        <v>-23.0038</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.953</v>
+        <v>-13.9672</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.1232</v>
+        <v>-12.1626</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8301999999999989</v>
+        <v>-1.8045</v>
       </c>
       <c r="G14" t="n">
-        <v>-26.8604</v>
+        <v>-5.9133</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.8842</v>
+        <v>3.2342</v>
       </c>
       <c r="I14" t="n">
-        <v>-15.9755</v>
+        <v>-9.147599999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>3.954000000000001</v>
+        <v>-0.2291999999999998</v>
       </c>
       <c r="K14" t="n">
-        <v>1.276100000000001</v>
+        <v>4.8874</v>
       </c>
       <c r="L14" t="n">
-        <v>2.6776</v>
+        <v>-5.1164</v>
       </c>
       <c r="M14" t="n">
-        <v>-30.8136</v>
+        <v>-5.6843</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.1606</v>
+        <v>-1.6532</v>
       </c>
       <c r="O14" t="n">
-        <v>-18.6536</v>
+        <v>-4.0308</v>
       </c>
       <c r="P14" t="n">
-        <v>5.335</v>
+        <v>9.999999999998899e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>-53.3492</v>
+        <v>-15.7731</v>
       </c>
       <c r="R14" t="n">
-        <v>58.6841</v>
+        <v>15.7733</v>
       </c>
       <c r="S14" t="n">
-        <v>-17.6194</v>
+        <v>0.9177999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-13.4208</v>
+        <v>-0.7641999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.1985</v>
+        <v>1.6823</v>
       </c>
       <c r="V14" t="n">
-        <v>21.1915</v>
+        <v>-8.9719</v>
       </c>
       <c r="W14" t="n">
-        <v>45.6929</v>
+        <v>4.6035</v>
       </c>
       <c r="X14" t="n">
-        <v>-24.5014</v>
+        <v>-13.5754</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. CORDINIER</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>-23.1107</v>
+        <v>-19.0416</v>
       </c>
       <c r="E15" t="n">
-        <v>-22.033</v>
+        <v>-28.3717</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0779</v>
+        <v>9.330399999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-10.7248</v>
+        <v>1.5142</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2534999999999994</v>
+        <v>-1.428</v>
       </c>
       <c r="I15" t="n">
-        <v>-10.9783</v>
+        <v>2.9416</v>
       </c>
       <c r="J15" t="n">
-        <v>13.8942</v>
+        <v>36.9599</v>
       </c>
       <c r="K15" t="n">
-        <v>14.8892</v>
+        <v>14.977</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.9946999999999995</v>
+        <v>21.9826</v>
       </c>
       <c r="M15" t="n">
-        <v>-24.6192</v>
+        <v>-35.4457</v>
       </c>
       <c r="N15" t="n">
-        <v>-14.6356</v>
+        <v>-16.4049</v>
       </c>
       <c r="O15" t="n">
-        <v>-9.9842</v>
+        <v>-19.0409</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.783400000000001</v>
+        <v>-22.9631</v>
       </c>
       <c r="Q15" t="n">
-        <v>-54.2771</v>
+        <v>-89.3017</v>
       </c>
       <c r="R15" t="n">
-        <v>51.4937</v>
+        <v>66.3386</v>
       </c>
       <c r="S15" t="n">
-        <v>-15.6415</v>
+        <v>4.6937</v>
       </c>
       <c r="T15" t="n">
-        <v>-10.6936</v>
+        <v>-0.8155999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.947500000000001</v>
+        <v>5.5094</v>
       </c>
       <c r="V15" t="n">
-        <v>6.0389</v>
+        <v>-2.2862</v>
       </c>
       <c r="W15" t="n">
-        <v>29.0427</v>
+        <v>24.785</v>
       </c>
       <c r="X15" t="n">
-        <v>-23.0038</v>
+        <v>-27.0712</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. SMITS</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>-32.5888</v>
+        <v>-26.0327</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.1698</v>
+        <v>-25.8802</v>
       </c>
       <c r="F16" t="n">
-        <v>-25.4192</v>
+        <v>-0.1523999999999996</v>
       </c>
       <c r="G16" t="n">
-        <v>-13.3912</v>
+        <v>-20.0242</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.7213</v>
+        <v>-13.5159</v>
       </c>
       <c r="I16" t="n">
-        <v>-10.6698</v>
+        <v>-6.508100000000002</v>
       </c>
       <c r="J16" t="n">
-        <v>15.036</v>
+        <v>0.2386000000000009</v>
       </c>
       <c r="K16" t="n">
-        <v>13.5968</v>
+        <v>-0.8031999999999997</v>
       </c>
       <c r="L16" t="n">
-        <v>1.4392</v>
+        <v>1.0414</v>
       </c>
       <c r="M16" t="n">
-        <v>-28.4275</v>
+        <v>-20.2627</v>
       </c>
       <c r="N16" t="n">
-        <v>-16.3182</v>
+        <v>-12.7127</v>
       </c>
       <c r="O16" t="n">
-        <v>-12.1091</v>
+        <v>-7.5495</v>
       </c>
       <c r="P16" t="n">
-        <v>8.350199999999999</v>
+        <v>-7.422499999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-36.4168</v>
+        <v>-36.4171</v>
       </c>
       <c r="R16" t="n">
-        <v>44.7672</v>
+        <v>28.9946</v>
       </c>
       <c r="S16" t="n">
-        <v>5.1849</v>
+        <v>-4.5453</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2511</v>
+        <v>-3.5924</v>
       </c>
       <c r="U16" t="n">
-        <v>3.9339</v>
+        <v>-0.9528000000000003</v>
       </c>
       <c r="V16" t="n">
-        <v>-32.7332</v>
+        <v>5.959299999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>12.9597</v>
+        <v>13.8901</v>
       </c>
       <c r="X16" t="n">
-        <v>-45.6929</v>
+        <v>-7.930800000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>R. SMITS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>-36.9784</v>
+        <v>-34.5798</v>
       </c>
       <c r="E17" t="n">
-        <v>-31.4315</v>
+        <v>-10.209</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.546600000000001</v>
+        <v>-24.371</v>
       </c>
       <c r="G17" t="n">
-        <v>-20.0242</v>
+        <v>-13.3912</v>
       </c>
       <c r="H17" t="n">
-        <v>-13.5159</v>
+        <v>-2.7213</v>
       </c>
       <c r="I17" t="n">
-        <v>-6.508100000000002</v>
+        <v>-10.6698</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2386000000000009</v>
+        <v>15.036</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8031999999999997</v>
+        <v>13.5968</v>
       </c>
       <c r="L17" t="n">
-        <v>1.0414</v>
+        <v>1.4392</v>
       </c>
       <c r="M17" t="n">
-        <v>-20.2627</v>
+        <v>-28.4275</v>
       </c>
       <c r="N17" t="n">
-        <v>-12.7127</v>
+        <v>-16.3182</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.5495</v>
+        <v>-12.1091</v>
       </c>
       <c r="P17" t="n">
-        <v>-7.422499999999999</v>
+        <v>8.350199999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>-36.4171</v>
+        <v>-36.4168</v>
       </c>
       <c r="R17" t="n">
-        <v>28.9946</v>
+        <v>44.7672</v>
       </c>
       <c r="S17" t="n">
-        <v>-15.4912</v>
+        <v>3.194</v>
       </c>
       <c r="T17" t="n">
-        <v>-9.143600000000001</v>
+        <v>-1.7888</v>
       </c>
       <c r="U17" t="n">
-        <v>-6.3475</v>
+        <v>4.9826</v>
       </c>
       <c r="V17" t="n">
-        <v>5.959299999999999</v>
+        <v>-32.7332</v>
       </c>
       <c r="W17" t="n">
-        <v>13.8901</v>
+        <v>12.9597</v>
       </c>
       <c r="X17" t="n">
-        <v>-7.930800000000001</v>
+        <v>-45.6929</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-76.3142</v>
+        <v>-65.9695</v>
       </c>
       <c r="E18" t="n">
-        <v>-57.3173</v>
+        <v>-51.8213</v>
       </c>
       <c r="F18" t="n">
-        <v>-18.9971</v>
+        <v>-14.1484</v>
       </c>
       <c r="G18" t="n">
         <v>-40.4008</v>
@@ -1858,13 +1858,13 @@
         <v>42.6795</v>
       </c>
       <c r="S18" t="n">
-        <v>-12.9441</v>
+        <v>-2.5998</v>
       </c>
       <c r="T18" t="n">
-        <v>-10.5451</v>
+        <v>-5.048999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.3993</v>
+        <v>2.4492</v>
       </c>
       <c r="V18" t="n">
         <v>-15.5469</v>
@@ -1891,22 +1891,22 @@
         <v>37</v>
       </c>
       <c r="D19" t="n">
-        <v>-166.8927</v>
+        <v>-123.0772</v>
       </c>
       <c r="E19" t="n">
-        <v>-107.1071</v>
+        <v>-95.53219999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-59.78609999999999</v>
+        <v>-27.5447</v>
       </c>
       <c r="G19" t="n">
-        <v>-45.20089999999999</v>
+        <v>-45.2009</v>
       </c>
       <c r="H19" t="n">
         <v>-22.36369999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-22.8371</v>
+        <v>-22.83710000000001</v>
       </c>
       <c r="J19" t="n">
         <v>274.9492</v>
@@ -1933,19 +1933,19 @@
         <v>-552.0505000000001</v>
       </c>
       <c r="R19" t="n">
-        <v>547.4125999999999</v>
+        <v>547.4126</v>
       </c>
       <c r="S19" t="n">
-        <v>-65.4175</v>
+        <v>-21.6015</v>
       </c>
       <c r="T19" t="n">
-        <v>-58.32749999999999</v>
+        <v>-46.7535</v>
       </c>
       <c r="U19" t="n">
-        <v>-7.088100000000001</v>
+        <v>25.1522</v>
       </c>
       <c r="V19" t="n">
-        <v>-51.63830000000001</v>
+        <v>-51.6383</v>
       </c>
       <c r="W19" t="n">
         <v>228.3152</v>
